--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2020_magallanes.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2020_magallanes.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-08 13:42</t>
+    <t xml:space="preserve">2026-09-09 20:01</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2020_magallanes.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2020_magallanes.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 20:01</t>
+    <t xml:space="preserve">2026-09-18 17:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2020_magallanes.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2020_magallanes.xlsx
@@ -30,39 +30,39 @@
     <t xml:space="preserve">Cobertura</t>
   </si>
   <si>
+    <t xml:space="preserve">Natales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Punta Arenas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cabo de Hornos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Primavera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Porvenir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antártica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Río Verde</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Laguna Blanca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Timaukel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Gregorio</t>
+  </si>
+  <si>
     <t xml:space="preserve">Torres del Paine</t>
   </si>
   <si>
-    <t xml:space="preserve">San Gregorio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Timaukel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Laguna Blanca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Río Verde</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Antártica</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Porvenir</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Primavera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cabo de Hornos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Punta Arenas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Natales</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 17:04</t>
+    <t xml:space="preserve">2026-09-27 21:47</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -492,13 +492,13 @@
         <v>4</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>181</v>
+        <v>26242</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1021</v>
+        <v>23782</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>17.73</v>
+        <v>110.34</v>
       </c>
     </row>
     <row r="3">
@@ -506,13 +506,13 @@
         <v>5</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>223</v>
+        <v>136875</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>681</v>
+        <v>141984</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>32.75</v>
+        <v>96.4</v>
       </c>
     </row>
     <row r="4">
@@ -520,13 +520,13 @@
         <v>6</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>127</v>
+        <v>1909</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>282</v>
+        <v>1983</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>45.04</v>
+        <v>96.27</v>
       </c>
     </row>
     <row r="5">
@@ -534,13 +534,13 @@
         <v>7</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>185</v>
+        <v>654</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>264</v>
+        <v>694</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>70.08</v>
+        <v>94.24</v>
       </c>
     </row>
     <row r="6">
@@ -548,13 +548,13 @@
         <v>8</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>150</v>
+        <v>6778</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>211</v>
+        <v>7323</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>71.09</v>
+        <v>92.56</v>
       </c>
     </row>
     <row r="7">
@@ -576,13 +576,13 @@
         <v>10</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>6778</v>
+        <v>150</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>7323</v>
+        <v>211</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>92.56</v>
+        <v>71.09</v>
       </c>
     </row>
     <row r="9">
@@ -590,13 +590,13 @@
         <v>11</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>654</v>
+        <v>185</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>694</v>
+        <v>264</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>94.24</v>
+        <v>70.08</v>
       </c>
     </row>
     <row r="10">
@@ -604,13 +604,13 @@
         <v>12</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>1909</v>
+        <v>127</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>1983</v>
+        <v>282</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>96.27</v>
+        <v>45.04</v>
       </c>
     </row>
     <row r="11">
@@ -618,13 +618,13 @@
         <v>13</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>136875</v>
+        <v>223</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>141984</v>
+        <v>681</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>96.4</v>
+        <v>32.75</v>
       </c>
     </row>
     <row r="12">
@@ -632,13 +632,13 @@
         <v>14</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>26242</v>
+        <v>181</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>23782</v>
+        <v>1021</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>110.34</v>
+        <v>17.73</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2020_magallanes.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2020_magallanes.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 21:47</t>
+    <t xml:space="preserve">2026-10-05 05:44</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
